--- a/artfynd/A 44733-2024 artfynd.xlsx
+++ b/artfynd/A 44733-2024 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>120288188</v>
       </c>
       <c r="B4" t="n">
-        <v>91128</v>
+        <v>91146</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 44733-2024 artfynd.xlsx
+++ b/artfynd/A 44733-2024 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>121150423</v>
       </c>
       <c r="B5" t="n">
-        <v>90973</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 44733-2024 artfynd.xlsx
+++ b/artfynd/A 44733-2024 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>121150423</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>90995</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 44733-2024 artfynd.xlsx
+++ b/artfynd/A 44733-2024 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>121150423</v>
       </c>
       <c r="B5" t="n">
-        <v>90995</v>
+        <v>90996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 44733-2024 artfynd.xlsx
+++ b/artfynd/A 44733-2024 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>121150423</v>
       </c>
       <c r="B5" t="n">
-        <v>90996</v>
+        <v>90999</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 44733-2024 artfynd.xlsx
+++ b/artfynd/A 44733-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97909340</v>
+        <v>118676896</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,14 +710,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Krokträsk, Nb</t>
+          <t>Stockfors, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776829.2504194332</v>
+        <v>776804</v>
       </c>
       <c r="R2" t="n">
-        <v>7305399.060683585</v>
+        <v>7305440</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,27 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676896</v>
+        <v>121150423</v>
       </c>
       <c r="B3" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,12 +801,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776804</v>
+        <v>776879</v>
       </c>
       <c r="R3" t="n">
-        <v>7305440</v>
+        <v>7305336</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -910,12 +890,7 @@
         <v>120288188</v>
       </c>
       <c r="B4" t="n">
-        <v>91198</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,117 +990,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>121150423</v>
-      </c>
-      <c r="B5" t="n">
-        <v>90999</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>658</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Stockfors, Nb</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>776879</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7305336</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Älvsbyn</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Älvsby</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44733-2024 artfynd.xlsx
+++ b/artfynd/A 44733-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676896</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150423</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,8 +1005,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288188</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>